--- a/pensum/ok01/OK01_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok01/OK01_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="156">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 1: Etablering og oppstart av egen bedrift (V5)</t>
   </si>
@@ -152,18 +152,48 @@
     <t xml:space="preserve">a)  Tenk deg at Nordlys var et AS uten kausjon. Hvor mye har Kari og Tom til sammen tapt av egne penger når boet er gjort opp? Tenk på hva de skjøt inn, og hva de skylder etterpå.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aksjonærenes ansvar er begrenset til innskutt aksjekapital (Økonomistyring 1.4), og etter konkurs er aksjonærer i AS fri sine forpliktelser (1.6). Minstekravet er 30 000 kr (1.4, aksjeloven § 3-1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Nå med kausjonen som banken faktisk krevde. Hvor mye kan banken kreve av Kari og Tom privat etter bobehandlingen?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kausjon: et personlig løfte om å betale en annens gjeld hvis skyldneren ikke kan. Begrepet er ikke forklart i kap. 1; boka nevner i 1.6 at selgeren kan ha «garantert for selskapets lån».</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Tenk deg at Nordlys var et DA med 50 % hver og ingen kausjon. Hva skylder Kari av den udekkede gjelden?</t>
   </si>
   <si>
+    <t xml:space="preserve">DA, delt ansvar: hver eier svarer bare for sin forholdsmessige andel, for eksempel 40 % av gjelden for den som eier 40 % (Økonomistyring 1.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Tenk deg at Nordlys var et ANS uten kausjon. Hvor mye av den udekkede gjelden kan kreditorene til sammen kreve av Kari alene?   A: 700 000 kr, hennes halvdel   B: 1 400 000 kr, hele gjelden   C: 0 kr, fordi selskapet er en egen enhet   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Kari eier et hus, Tom leier. Var aksjeselskap riktig valg for dem, når banken likevel krevde kausjon? Skriv to setninger: én om hva AS skjermer dem mot, og én om hva de bør forhandle med banken om.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Bruk tabell 1.1 (fordeler og ulemper ved foretaksformene) og ansvarsreglene i 1.2–1.4 og 1.6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS med og uten kausjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I AS er innskuddet tapt, men eierne skylder ikke noe etterpå. Kausjonen gjelder bare banklånet: det banken mangler, kan den kreve av Kari og Tom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANS eller DA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DA: gjelden × eierandelen. ANS: solidarisk, så hver eier kan kreves for hele gjelden. Kari kan etterpå kreve Tom for hans del.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 1, avsnitt 1.2–1.4, 1.6 og tabell 1.1. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -224,9 +254,15 @@
     <t xml:space="preserve">a)  Fjell Elektro er et AS, og Mona har kausjonert for banklånet. Hvor mye kan hun til sammen tape privat: det hun skjøt inn, pluss det banken kan kreve etter bobehandlingen?</t>
   </si>
   <si>
+    <t xml:space="preserve">Ansvaret i AS er begrenset til innskutt aksjekapital (Økonomistyring 1.4). Kausjonen kommer i tillegg og gjelder bare det lånet den er gitt for (kausjon er ikke forklart i boka; se A1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Tenk deg at Mona hadde startet som enkeltpersonforetak. Hva skylder hun etter bobehandlingen?</t>
   </si>
   <si>
+    <t xml:space="preserve">I et enkeltpersonforetak er eieren fullt ansvarlig for gjelden med hele sin formue (Økonomistyring 1.2). Etter konkurs skylder eiere av EPF fortsatt det udekkede beløpet (1.6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvilket år kunne Mona tidligst stå som faglig ansvarlig for et foretak som bygger og vedlikeholder andres anlegg? Bruk FEK § 7.   A: 2019, rett etter fagskolen   B: 2022, da hun hadde tre års praksis etter fagskolen   C: 2023, da hun også hadde bestått prøven   (skriv bokstaven)</t>
   </si>
   <si>
@@ -251,6 +287,18 @@
     <t xml:space="preserve">e)  Mona eier alene, og enkeltpersonforetak er enklere og billigere. Hvorfor bør Fjell Elektro likevel være AS? Gi to argumenter og ett motargument.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Tabell 1.1 (fordeler og ulemper) og 1.4 (AS er foretrukket når verdier, ansatte og belåning er betydelige).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tre vilkår: utdanning, minst tre års relevant praksis etter utdanningen, og bestått prøve for andres anlegg. Året da det siste vilkåret ble oppfylt, avgjør.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva Mona risikerer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS: aksjekapitalen + det banken mangler på lånet hun har kausjonert for. Enkeltpersonforetak: hele den udekkede gjelden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 1, avsnitt 1.2 og 1.4. Forskrift om elektroforetak og kvalifikasjonskrav (FEK), FOR-2013-06-19-739, § 3, § 5 og § 7 (gjengitt av DSB og installatorproven.no, hentet 11.10.2026). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -302,9 +350,15 @@
     <t xml:space="preserve">a)  Egenkapitalen justert til virkelige verdier, i kroner: virkelig verdi av eiendelene minus all gjeld.</t>
   </si>
   <si>
+    <t xml:space="preserve">Justert egenkapital = virkelig verdi av eiendelene − gjeld. Prisen ved salg av AS tar utgangspunkt i bokført egenkapital justert for virkelige (markedsmessige) verdier (Økonomistyring 1.6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mye betaler konsernet for goodwill? Budet minus justert egenkapital.</t>
   </si>
   <si>
+    <t xml:space="preserve">Goodwill = det kjøperen betaler ut over verdien av eiendelene, et overskuddspotensial som ikke står i balansen (Økonomistyring 1.6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Konsernet kjøper aksjene. Hva overtar det?   A: Alle eiendeler og all gjeld   B: Bare de eiendelene partene avtaler   C: Bare kundekretsen og navnet   (skriv bokstaven)</t>
   </si>
   <si>
@@ -329,6 +383,21 @@
     <t xml:space="preserve">e)  Er budet godt? Skriv to setninger om hva goodwillen betaler for, og hva Kari og Tom bør sjekke før de sier ja.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Goodwill og vilkårene ved salg av AS i Økonomistyring 1.6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justert egenkapital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summer virkelig verdi av eiendelene. Trekk fra all gjeld, 7 290 000. Goodwill er budet minus det tallet, ikke minus bokført egenkapital.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Påstandene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Én revisjonsgrense over er nok. Goodwill finnes bare ved et faktisk salg. Fusjon slår sammen, fisjon deler opp.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 1, avsnitt 1.4, 1.6 og 1.7. Balansen er Nordlys' balanse 31.12. (faktaarket, kap. 3). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -374,9 +443,15 @@
     <t xml:space="preserve">a)  Hvor mye mer betalte Mona i gebyr for å registrere et AS enn hun hadde betalt for et enkeltpersonforetak bare i Enhetsregisteret?</t>
   </si>
   <si>
+    <t xml:space="preserve">ANS/DA og AS skal registreres i Foretaksregisteret, EPF i Enhetsregisteret og eventuelt i tillegg i Foretaksregisteret (Økonomistyring 1.7). Gebyrene er fra brreg.no (2026); boka sier at EPF registreres gratis, og det er endret.</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange kroner kan driftsinntektene øke før Fjell Elektro passerer grensen på 7 millioner?</t>
   </si>
   <si>
+    <t xml:space="preserve">Revisjonsplikten faller bort når driftsinntektene er under 7 millioner, eiendelene under 27 millioner og årsverkene ikke over 10 (Økonomistyring 1.4, aksjeloven § 7-6).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Fjell kan ikke betale grossisten ved forfall i mars, men en ordre på 600 000 betales om fem uker. Hva bør Mona gjøre først?   A: Begjære konkurs straks, fordi en regning ikke er betalt ved forfall   B: Forhandle med grossisten og banken om utsettelse, fordi problemet kan være forbigående   C: Melde opphør til Brønnøysundregistrene   (skriv bokstaven)</t>
   </si>
   <si>
@@ -399,6 +474,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Mona vil velge bort revisor for å spare penger. Skriv to setninger: hva som må til, og hva som taler for og mot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisjonsgrensene i Økonomistyring 1.4. Fravalg av revisjon: aksjeloven § 7-6 (ikke beskrevet i boka). Regnskapsplikt: 1.5 og regnskapsloven § 1-2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forbigående eller ikke?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plikten til å begjære konkurs gjelder når problemene ikke er forbigående og verdiene ikke dekker gjelden. Kommer pengene om fem uker?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvem skylder hva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS: ingenting etterpå, bortsett fra kausjonen. ENK: alt. DA: andelen. ANS: hele beløpet kan kreves av én eier.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 1, avsnitt 1.4–1.7. Gebyrer: brreg.no/bedrift/gebyr (2026), hentet 11.10.2026. Fravalg av revisjon: aksjeloven § 7-6. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -412,7 +502,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,8 +569,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -501,8 +613,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -555,7 +685,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -604,11 +734,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -628,19 +778,19 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -673,8 +823,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -688,7 +838,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -702,7 +852,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1005,7 +1155,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1166,35 +1316,20 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+    <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="11" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(700000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="B17" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(700000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
         <v>44</v>
       </c>
@@ -1202,72 +1337,176 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="12"/>
+      <c r="F19" s="10"/>
       <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F19="","",IF(ABS(F19-(700000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(700000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>47</v>
+      </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+    <row r="25" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="11" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="25">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1279,13 +1518,20 @@
     <mergeCell ref="B13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1302,7 +1548,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1313,7 +1559,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1323,7 +1569,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1334,7 +1580,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1358,10 +1604,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1371,10 +1617,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1384,10 +1630,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1397,10 +1643,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1410,10 +1656,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1423,10 +1669,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1436,10 +1682,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1464,7 +1710,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1476,173 +1722,249 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(1100000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="C","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
+      <c r="F20" s="10"/>
+      <c r="G20" s="11" t="str">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(1100000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="C","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="11" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="14"/>
       <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="11" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1655,18 +1977,24 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1683,7 +2011,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1694,7 +2022,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1704,7 +2032,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1715,7 +2043,7 @@
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1725,103 +2053,103 @@
       <c r="G5" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>81</v>
+      <c r="A7" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="17" t="n">
+      <c r="A8" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <v>1200000</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="22" t="n">
         <v>1200000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="19" t="n">
+      <c r="A9" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B9" s="24" t="n">
         <v>2400000</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="24" t="n">
         <v>2100000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="17" t="n">
+      <c r="A10" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="22" t="n">
         <v>1400000</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="22" t="n">
         <v>1350000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="19" t="n">
+      <c r="A11" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="24" t="n">
         <v>4200000</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="24" t="n">
         <v>4200000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="17" t="n">
+      <c r="A12" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="22" t="n">
         <v>982650</v>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="22" t="n">
         <v>982650</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="21" t="n">
+      <c r="A13" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13" s="26" t="n">
         <v>10182650</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="17" t="n">
+      <c r="A14" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" s="22" t="n">
         <v>7290000</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="22" t="n">
         <v>7290000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B15" s="21" t="n">
+      <c r="A15" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="26" t="n">
         <v>2892650</v>
       </c>
       <c r="C15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1847,7 +2175,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1859,190 +2187,272 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(1457350))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="A","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(1457350))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="11" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="12"/>
+      <c r="F25" s="14"/>
       <c r="G25" s="11" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="A","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="12"/>
+      <c r="F27" s="14"/>
       <c r="G27" s="11" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="11" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="11" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="11" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="23">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A18:E18"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2059,7 +2469,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2070,7 +2480,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2080,7 +2490,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2091,7 +2501,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2115,10 +2525,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2128,10 +2538,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2141,10 +2551,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2154,10 +2564,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2167,10 +2577,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2195,7 +2605,7 @@
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2207,173 +2617,249 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11" t="str">
-        <f aca="false">IF(F16="","",IF(ABS(F16-(2205000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="11" t="str">
-        <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11" t="str">
+        <f aca="false">IF(F18="","",IF(ABS(F18-(2205000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="11" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="12"/>
+      <c r="F21" s="14"/>
       <c r="G21" s="11" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="11" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="14"/>
       <c r="G23" s="11" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-    </row>
-    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="11" t="str">
+        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="11" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="11" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="11" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="28">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2384,18 +2870,24 @@
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="B16:G16"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:G27"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ok01/OK01_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok01/OK01_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="157">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 1: Etablering og oppstart av egen bedrift (V5)</t>
   </si>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">25 minutter · Helst alene. Sammen med sidemannen eller flere hvis du vil. Ark og blyant, appen (PC eller mobil) eller læreboka.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Selskapsformen avgjør hvem som betaler når bedriften ikke kan. I et enkeltpersonforetak hefter eieren for all gjeld med hele formuen sin. I et ANS hefter hver eier for hele gjelden (solidarisk), i et DA for sin andel. I et aksjeselskap taper eierne aksjekapitalen, men ikke mer. En personlig kausjon er et eget løfte til banken, og den gjelder uansett selskapsform.</t>
+    <t xml:space="preserve">Kort oppsummert: Selskapsformen avgjør hvem som betaler når bedriften ikke kan. I et enkeltpersonforetak hefter eieren for all gjeld med hele formuen sin. I et ansvarlig selskap (ANS) hefter hver eier for hele gjelden (solidarisk), i et selskap med delt ansvar (DA) for sin andel. I et aksjeselskap taper eierne aksjekapitalen, men ikke mer. En personlig kausjon er et eget løfte til banken, og den gjelder uansett selskapsform.</t>
   </si>
   <si>
     <t xml:space="preserve">Det er 2019. Kari Nordlund (elektroinstallatør) og Tom Berg (elektriker) starter Nordlys Elektro AS og eier halvparten hver. De skyter inn 300 000 kr i aksjekapital. Banken låner dem 877 500 kr, men krever personlig kausjon fra begge. Tenk deg nå at første driftsår går galt og Nordlys går konkurs. Når boet er gjort opp, står det igjen 1 400 000 kr i udekket gjeld: 700 000 til banken og 700 000 til grossisten Polarlys. Regn ut hva Kari og Tom sitter igjen med i hver selskapsform. Gå fram slik: hva er tapt allerede (innskuddet), hva kan kreves av eierne etterpå, og hvem kan kreves for hva.</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">I c og d</t>
   </si>
   <si>
-    <t xml:space="preserve">Tenk deg DA og ANS uten kausjon, samme gjeld og eierandeler</t>
+    <t xml:space="preserve">Tenk deg selskap med delt ansvar (DA) og ansvarlig selskap (ANS) uten kausjon, samme gjeld og eierandeler</t>
   </si>
   <si>
     <t xml:space="preserve">Deloppgave</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">Kausjon: et personlig løfte om å betale en annens gjeld hvis skyldneren ikke kan. Begrepet er ikke forklart i kap. 1; boka nevner i 1.6 at selgeren kan ha «garantert for selskapets lån».</t>
   </si>
   <si>
-    <t xml:space="preserve">c)  Tenk deg at Nordlys var et DA med 50 % hver og ingen kausjon. Hva skylder Kari av den udekkede gjelden?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DA, delt ansvar: hver eier svarer bare for sin forholdsmessige andel, for eksempel 40 % av gjelden for den som eier 40 % (Økonomistyring 1.3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d)  Tenk deg at Nordlys var et ANS uten kausjon. Hvor mye av den udekkede gjelden kan kreditorene til sammen kreve av Kari alene?   A: 700 000 kr, hennes halvdel   B: 1 400 000 kr, hele gjelden   C: 0 kr, fordi selskapet er en egen enhet   (skriv bokstaven)</t>
+    <t xml:space="preserve">c)  Tenk deg at Nordlys var et selskap med delt ansvar (DA) med 50 % hver og ingen kausjon. Hva skylder Kari av den udekkede gjelden?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selskap med delt ansvar (DA), delt ansvar: hver eier svarer bare for sin forholdsmessige andel, for eksempel 40 % av gjelden for den som eier 40 % (Økonomistyring 1.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d)  Tenk deg at Nordlys var et ansvarlig selskap (ANS) uten kausjon. Hvor mye av den udekkede gjelden kan kreditorene til sammen kreve av Kari alene?   A: 700 000 kr, hennes halvdel   B: 1 400 000 kr, hele gjelden   C: 0 kr, fordi selskapet er en egen enhet   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Kari eier et hus, Tom leier. Var aksjeselskap riktig valg for dem, når banken likevel krevde kausjon? Skriv to setninger: én om hva AS skjermer dem mot, og én om hva de bør forhandle med banken om.</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">I AS er innskuddet tapt, men eierne skylder ikke noe etterpå. Kausjonen gjelder bare banklånet: det banken mangler, kan den kreve av Kari og Tom.</t>
   </si>
   <si>
-    <t xml:space="preserve">ANS eller DA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DA: gjelden × eierandelen. ANS: solidarisk, så hver eier kan kreves for hele gjelden. Kari kan etterpå kreve Tom for hans del.</t>
+    <t xml:space="preserve">Solidarisk eller delt ansvar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selskap med delt ansvar (DA): gjelden × eierandelen. Ansvarlig selskap (ANS): solidarisk, så hver eier kan kreves for hele gjelden. Kari kan etterpå kreve Tom for hans del.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 1, avsnitt 1.2–1.4, 1.6 og tabell 1.1. Nordlys Elektro AS er en konstruert casebedrift.</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">A2 · Fjell Elektro: kan Mona starte, og hva risikerer hun?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: Før selskapsformen kommer retten til å tilby arbeidet. Et elektroforetak må være registrert i Elvirksomhetsregisteret med en faglig ansvarlig (FEK § 3). Faglig ansvarlig skal være fast ansatt og tilgjengelig i foretakets normale arbeidstid (§ 5), og for arbeid på andres anlegg ha relevant utdanning, minst tre års relevant praksis etter endt utdanning og bestått elektroinstallatørprøve (§ 7). Så selskapsformen: i et AS taper eieren aksjekapitalen og det hun har kausjonert for; i et enkeltpersonforetak skylder hun alt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mona Fjell vil starte Fjell Elektro AS i Oslo med to montører, og selv være daglig leder og faglig ansvarlig og jobbe halve tiden ute på oppdrag. Hun skyter inn 300 000 kr i aksjekapital og låner 500 000 kr i banken, som krever personlig kausjon fra henne. Først: fyller hun kravene i FEK? Så: tenk deg at det går galt i år 3 og Fjell Elektro går konkurs. Da er 1 100 000 kr udekket etter bobehandlingen, og 300 000 kr av det er restlånet i banken. Hva risikerer Mona privat i AS, og hva hadde det vært i et enkeltpersonforetak?</t>
+    <t xml:space="preserve">Kort oppsummert: Før selskapsformen kommer retten til å tilby arbeidet. Et elektroforetak må være registrert i Elvirksomhetsregisteret med en faglig ansvarlig (forskrift om elektroforetak og kvalifikasjonskrav § 3). Faglig ansvarlig skal være fast ansatt og tilgjengelig i foretakets normale arbeidstid (§ 5), og for arbeid på andres anlegg ha relevant utdanning, minst tre års relevant praksis etter endt utdanning og bestått elektroinstallatørprøve (§ 7). Så selskapsformen: i et AS taper eieren aksjekapitalen og det hun har kausjonert for; i et enkeltpersonforetak skylder hun alt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mona Fjell vil starte Fjell Elektro AS i Oslo med to montører, og selv være daglig leder og faglig ansvarlig og jobbe halve tiden ute på oppdrag. Hun skyter inn 300 000 kr i aksjekapital og låner 500 000 kr i banken, som krever personlig kausjon fra henne. Først: fyller hun kravene i forskrift om elektroforetak og kvalifikasjonskrav? Så: tenk deg at det går galt i år 3 og Fjell Elektro går konkurs. Da er 1 100 000 kr udekket etter bobehandlingen, og 300 000 kr av det er restlånet i banken. Hva risikerer Mona privat i AS, og hva hadde det vært i et enkeltpersonforetak?</t>
   </si>
   <si>
     <t xml:space="preserve">Mona, før fagskolen</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">Udekket gjeld 1 100 000 kr, av det restlånet 300 000</t>
   </si>
   <si>
-    <t xml:space="preserve">FEK § 7</t>
+    <t xml:space="preserve">Krav til faglig ansvarlig</t>
   </si>
   <si>
     <t xml:space="preserve">Utdanning + 3 års relevant praksis etter utdanningen + prøven</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">b)  Tenk deg at Mona hadde startet som enkeltpersonforetak. Hva skylder hun etter bobehandlingen?</t>
   </si>
   <si>
-    <t xml:space="preserve">I et enkeltpersonforetak er eieren fullt ansvarlig for gjelden med hele sin formue (Økonomistyring 1.2). Etter konkurs skylder eiere av EPF fortsatt det udekkede beløpet (1.6).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c)  Hvilket år kunne Mona tidligst stå som faglig ansvarlig for et foretak som bygger og vedlikeholder andres anlegg? Bruk FEK § 7.   A: 2019, rett etter fagskolen   B: 2022, da hun hadde tre års praksis etter fagskolen   C: 2023, da hun også hadde bestått prøven   (skriv bokstaven)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d)  Er dette i orden etter FEK? Svar ja eller nei for hver påstand, med paragrafen.</t>
+    <t xml:space="preserve">I et enkeltpersonforetak er eieren fullt ansvarlig for gjelden med hele sin formue (Økonomistyring 1.2). Etter konkurs skylder eiere av enkeltpersonforetak fortsatt det udekkede beløpet (1.6).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c)  Hvilket år kunne Mona tidligst stå som faglig ansvarlig for et foretak som bygger og vedlikeholder andres anlegg? Bruk forskrift om elektroforetak og kvalifikasjonskrav § 7.   A: 2019, rett etter fagskolen   B: 2022, da hun hadde tre års praksis etter fagskolen   C: 2023, da hun også hadde bestått prøven   (skriv bokstaven)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d)  Er dette i orden etter forskrift om elektroforetak og kvalifikasjonskrav? Svar ja eller nei for hver påstand, med paragrafen.</t>
   </si>
   <si>
     <t xml:space="preserve">      Mona er fast ansatt som faglig ansvarlig og jobber halve tiden ute på foretakets egne oppdrag   (Ja eller Nei)</t>
@@ -290,6 +290,9 @@
     <t xml:space="preserve">Ingen ny formel. Tabell 1.1 (fordeler og ulemper) og 1.4 (AS er foretrukket når verdier, ansatte og belåning er betydelige).</t>
   </si>
   <si>
+    <t xml:space="preserve">Kravene til faglig ansvarlig</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tre vilkår: utdanning, minst tre års relevant praksis etter utdanningen, og bestått prøve for andres anlegg. Året da det siste vilkåret ble oppfylt, avgjør.</t>
   </si>
   <si>
@@ -299,7 +302,7 @@
     <t xml:space="preserve">AS: aksjekapitalen + det banken mangler på lånet hun har kausjonert for. Enkeltpersonforetak: hele den udekkede gjelden.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 1, avsnitt 1.2 og 1.4. Forskrift om elektroforetak og kvalifikasjonskrav (FEK), FOR-2013-06-19-739, § 3, § 5 og § 7 (gjengitt av DSB og installatorproven.no, hentet 11.10.2026). Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 1, avsnitt 1.2 og 1.4. Forskrift om elektroforetak og kvalifikasjonskrav (FEK), FOR-2013-06-19-739, § 3, § 5 og § 7 (gjengitt av Direktoratet for samfunnssikkerhet og beredskap og installatorproven.no, hentet 11.10.2026). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: et bud på aksjene, og hva det betaler for</t>
@@ -404,7 +407,7 @@
     <t xml:space="preserve">B2 · Fjell Elektro: registrert, regnskapspliktig, og når pengene tar slutt</t>
   </si>
   <si>
-    <t xml:space="preserve">Kort oppsummert: ANS, DA og AS skal i Foretaksregisteret; et enkeltpersonforetak registreres i Enhetsregisteret og kan i tillegg stå i Foretaksregisteret. Et AS er alltid regnskapspliktig, men slipper revisor når det er under alle tre grensene: 7 millioner i driftsinntekter, 27 millioner i eiendeler og 10 årsverk. Kan bedriften ikke betale, er konkurs siste steg: først forhandling med kreditorene, styrt avvikling eller akkord. Etter konkurs skylder eiere av EPF og ANS/DA fortsatt det udekkede; aksjonærene i AS er fri, med mindre de har kausjonert.</t>
+    <t xml:space="preserve">Kort oppsummert: Ansvarlig selskap (ANS), selskap med delt ansvar (DA) og AS skal i Foretaksregisteret; et enkeltpersonforetak registreres i Enhetsregisteret og kan i tillegg stå i Foretaksregisteret. Et AS er alltid regnskapspliktig, men slipper revisor når det er under alle tre grensene: 7 millioner i driftsinntekter, 27 millioner i eiendeler og 10 årsverk. Kan bedriften ikke betale, er konkurs siste steg: først forhandling med kreditorene, styrt avvikling eller akkord. Etter konkurs skylder eiere av enkeltpersonforetak og ansvarlige selskaper (solidarisk eller delt ansvar) fortsatt det udekkede; aksjonærene i AS er fri, med mindre de har kausjonert.</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i A2) ble registrert i Brønnøysund og har gått ett år med 4 795 000 kr i driftsinntekter, tre årsverk og under 2 millioner kroner i eiendeler. Først registrering og revisjon. Så år 3: en stor kunde har sagt opp avtalen, og i mars kan ikke Fjell betale grossisten ved forfall. En ordre på 600 000 kr betales om fem uker. Til slutt en tenkt konkurs der 900 000 kr er udekket, hvorav 300 000 er restlånet Mona har kausjonert for.</t>
@@ -413,7 +416,7 @@
     <t xml:space="preserve">Gebyr 2026, elektronisk</t>
   </si>
   <si>
-    <t xml:space="preserve">AS 6 825 · ENK i Enhetsregisteret 2 181 · ENK også i Foretaksregisteret 3 883</t>
+    <t xml:space="preserve">AS 6 825 · Enkeltpersonforetak i Enhetsregisteret 2 181 · Enkeltpersonforetak også i Foretaksregisteret 3 883</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro, år 1</t>
@@ -443,7 +446,7 @@
     <t xml:space="preserve">a)  Hvor mye mer betalte Mona i gebyr for å registrere et AS enn hun hadde betalt for et enkeltpersonforetak bare i Enhetsregisteret?</t>
   </si>
   <si>
-    <t xml:space="preserve">ANS/DA og AS skal registreres i Foretaksregisteret, EPF i Enhetsregisteret og eventuelt i tillegg i Foretaksregisteret (Økonomistyring 1.7). Gebyrene er fra brreg.no (2026); boka sier at EPF registreres gratis, og det er endret.</t>
+    <t xml:space="preserve">Ansvarlige selskaper (solidarisk eller delt ansvar) og AS skal registreres i Foretaksregisteret, enkeltpersonforetak i Enhetsregisteret og eventuelt i tillegg i Foretaksregisteret (Økonomistyring 1.7). Gebyrene er fra brreg.no (2026); boka sier at enkeltpersonforetak registreres gratis, og det er endret.</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Hvor mange kroner kan driftsinntektene øke før Fjell Elektro passerer grensen på 7 millioner?</t>
@@ -467,10 +470,10 @@
     <t xml:space="preserve">      Som enkeltpersonforetak skylder Mona alle 900 000   (Ja eller Nei)</t>
   </si>
   <si>
-    <t xml:space="preserve">      Hadde Mona og en partner drevet DA med 50 % hver, skylder hver 900 000   (Ja eller Nei)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Hadde de drevet ANS, kan kreditorene bare kreve halvparten av Mona   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Hadde Mona og en partner drevet selskap med delt ansvar (DA) med 50 % hver, skylder hver 900 000   (Ja eller Nei)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Hadde de drevet ansvarlig selskap (ANS), kan kreditorene bare kreve halvparten av Mona   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Mona vil velge bort revisor for å spare penger. Skriv to setninger: hva som må til, og hva som taler for og mot.</t>
@@ -488,7 +491,7 @@
     <t xml:space="preserve">Hvem skylder hva</t>
   </si>
   <si>
-    <t xml:space="preserve">AS: ingenting etterpå, bortsett fra kausjonen. ENK: alt. DA: andelen. ANS: hele beløpet kan kreves av én eier.</t>
+    <t xml:space="preserve">AS: ingenting etterpå, bortsett fra kausjonen. Enkeltpersonforetak: alt. Selskap med delt ansvar (DA): andelen. Ansvarlig selskap (ANS): hele beløpet kan kreves av én eier.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 1, avsnitt 1.4–1.7. Gebyrer: brreg.no/bedrift/gebyr (2026), hentet 11.10.2026. Fravalg av revisjon: aksjeloven § 7-6. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -1274,7 +1277,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
         <v>36</v>
       </c>
@@ -1567,7 +1570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>59</v>
       </c>
@@ -1578,7 +1581,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>60</v>
       </c>
@@ -1749,7 +1752,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
         <v>42</v>
       </c>
@@ -1762,7 +1765,7 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
     </row>
-    <row r="23" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
         <v>79</v>
       </c>
@@ -1776,7 +1779,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
         <v>80</v>
       </c>
@@ -1917,10 +1920,10 @@
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
@@ -1930,10 +1933,10 @@
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
@@ -1941,9 +1944,9 @@
       <c r="F39" s="18"/>
       <c r="G39" s="18"/>
     </row>
-    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -2022,7 +2025,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2032,7 +2035,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2043,7 +2046,7 @@
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2054,18 +2057,18 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" s="22" t="n">
         <v>1200000</v>
@@ -2076,7 +2079,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>2400000</v>
@@ -2087,7 +2090,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" s="22" t="n">
         <v>1400000</v>
@@ -2098,7 +2101,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" s="24" t="n">
         <v>4200000</v>
@@ -2109,7 +2112,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B12" s="22" t="n">
         <v>982650</v>
@@ -2120,7 +2123,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" s="26" t="n">
         <v>10182650</v>
@@ -2129,7 +2132,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" s="22" t="n">
         <v>7290000</v>
@@ -2140,7 +2143,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B15" s="26" t="n">
         <v>2892650</v>
@@ -2149,7 +2152,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -2175,7 +2178,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -2192,7 +2195,7 @@
         <v>42</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -2202,7 +2205,7 @@
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2219,7 +2222,7 @@
         <v>42</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -2229,7 +2232,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2243,7 +2246,7 @@
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2252,7 +2255,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -2266,7 +2269,7 @@
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2280,7 +2283,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2294,7 +2297,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -2308,7 +2311,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -2322,7 +2325,7 @@
     </row>
     <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -2361,7 +2364,7 @@
         <v>42</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C36" s="13"/>
       <c r="D36" s="13"/>
@@ -2382,10 +2385,10 @@
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
@@ -2395,10 +2398,10 @@
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C41" s="18"/>
       <c r="D41" s="18"/>
@@ -2408,7 +2411,7 @@
     </row>
     <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -2480,7 +2483,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2488,9 +2491,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2501,7 +2504,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2523,12 +2526,12 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2538,10 +2541,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2551,10 +2554,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2564,10 +2567,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2577,10 +2580,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2605,7 +2608,7 @@
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2617,12 +2620,12 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
         <v>42</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
@@ -2632,7 +2635,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2649,7 +2652,7 @@
         <v>42</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
@@ -2659,7 +2662,7 @@
     </row>
     <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -2673,7 +2676,7 @@
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -2682,7 +2685,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2696,7 +2699,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2710,7 +2713,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2722,9 +2725,9 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2736,9 +2739,9 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
@@ -2752,7 +2755,7 @@
     </row>
     <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2791,7 +2794,7 @@
         <v>42</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C32" s="13"/>
       <c r="D32" s="13"/>
@@ -2812,10 +2815,10 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -2825,10 +2828,10 @@
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -2838,7 +2841,7 @@
     </row>
     <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>

--- a/pensum/ok01/OK01_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok01/OK01_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="157">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 1: Etablering og oppstart av egen bedrift (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 1: Etablering og oppstart av egen bedrift (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>
